--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20212.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -692,16 +701,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="E4">
-        <v>28</v>
+        <v>9</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>67.86</v>
+      </c>
+      <c r="H4">
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -738,16 +750,19 @@
         <v>16</v>
       </c>
       <c r="D6">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="E6">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>87.5</v>
+      </c>
+      <c r="H6">
+        <v>8.5</v>
       </c>
     </row>
   </sheetData>
@@ -864,7 +879,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -907,16 +922,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -956,6 +971,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920382</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20212.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
   <si>
     <t>Mat</t>
   </si>
@@ -79,10 +79,28 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>ELPIDIO</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
     <t>SALAZAR</t>
   </si>
   <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARYFER</t>
+  </si>
+  <si>
+    <t>MIROSLAVA</t>
   </si>
   <si>
     <t>LUIS GUILLERMO</t>
@@ -655,16 +673,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>35</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>51.43</v>
+      </c>
+      <c r="H2">
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -678,16 +699,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="E3">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>48.65</v>
+      </c>
+      <c r="H3">
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -701,7 +725,7 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4">
         <v>9</v>
@@ -713,7 +737,7 @@
         <v>67.86</v>
       </c>
       <c r="H4">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -727,16 +751,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="E5">
-        <v>41</v>
+        <v>19</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>53.66</v>
+      </c>
+      <c r="H5">
+        <v>9.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -827,7 +854,7 @@
         <v>82.86</v>
       </c>
       <c r="H2">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -853,7 +880,7 @@
         <v>94.59</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -905,7 +932,7 @@
         <v>87.8</v>
       </c>
       <c r="H5">
-        <v>8.699999999999999</v>
+        <v>8.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -941,7 +968,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -973,24 +1000,70 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>21330051920382</v>
+        <v>21330051920108</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>21330051920078</v>
+      </c>
+      <c r="B3" t="s">
         <v>21</v>
       </c>
-      <c r="D2" t="s">
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>21330051920382</v>
+      </c>
+      <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
+      <c r="C4" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" t="s">
         <v>13</v>
       </c>
-      <c r="G2">
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20212.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
   <si>
     <t>Mat</t>
   </si>
@@ -77,33 +77,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ELPIDIO</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MARYFER</t>
-  </si>
-  <si>
-    <t>MIROSLAVA</t>
-  </si>
-  <si>
-    <t>LUIS GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -673,19 +646,19 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>51.43</v>
+        <v>82.86</v>
       </c>
       <c r="H2">
-        <v>9.699999999999999</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -699,19 +672,19 @@
         <v>37</v>
       </c>
       <c r="D3">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>18</v>
+        <v>34</v>
       </c>
       <c r="G3">
-        <v>48.65</v>
+        <v>91.89</v>
       </c>
       <c r="H3">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -725,19 +698,19 @@
         <v>28</v>
       </c>
       <c r="D4">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>67.86</v>
+        <v>92.86</v>
       </c>
       <c r="H4">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -751,19 +724,19 @@
         <v>41</v>
       </c>
       <c r="D5">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F5">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G5">
-        <v>53.66</v>
+        <v>87.8</v>
       </c>
       <c r="H5">
-        <v>9.4</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -777,16 +750,16 @@
         <v>16</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>1</v>
       </c>
-      <c r="E6">
-        <v>2</v>
-      </c>
       <c r="F6">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H6">
         <v>8.5</v>
@@ -845,16 +818,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G2">
-        <v>82.86</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="H2">
-        <v>8.800000000000001</v>
+        <v>8.699999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -871,16 +844,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="G3">
-        <v>94.59</v>
+        <v>100</v>
       </c>
       <c r="H3">
-        <v>8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -906,7 +879,7 @@
         <v>96.43000000000001</v>
       </c>
       <c r="H4">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -923,16 +896,16 @@
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F5">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="G5">
-        <v>87.8</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -949,16 +922,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6">
-        <v>93.75</v>
+        <v>100</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
+        <v>8.1</v>
       </c>
     </row>
   </sheetData>
@@ -968,7 +941,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -998,75 +971,6 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>21330051920108</v>
-      </c>
-      <c r="B2" t="s">
-        <v>20</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>21330051920078</v>
-      </c>
-      <c r="B3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>21330051920382</v>
-      </c>
-      <c r="B4" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" t="s">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Contreras Díaz Irma Ivette - Estadisticos 20212.xlsx
+++ b/docentes/Contreras Díaz Irma Ivette - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="23">
   <si>
     <t>Mat</t>
   </si>
@@ -77,6 +77,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>VASQUEZ</t>
+  </si>
+  <si>
+    <t>MONTIEL</t>
+  </si>
+  <si>
+    <t>CESAR DANIEL</t>
   </si>
 </sst>
 </file>
@@ -941,7 +950,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -971,6 +980,29 @@
         <v>19</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920133</v>
+      </c>
+      <c r="B2" t="s">
+        <v>20</v>
+      </c>
+      <c r="C2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
